--- a/public/FomaPrint-Price-List.xlsx
+++ b/public/FomaPrint-Price-List.xlsx
@@ -716,7 +716,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Weight in lbs. Box size = single-unit shipping box (as listed on fomaprint.com). Total = blank + front engraving + handling. Back engraving optional (+$2).</t>
+          <t>Weight in lbs. Box size = single-unit shipping box (as listed on fomaprint.com). Total = blank + front engraving + handling. Back engraving optional (+$3).</t>
         </is>
       </c>
     </row>
